--- a/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/01_FR1 - Günlük Toplantı ve Görsel Yönetim/EKG-LOJ-PNO-01_gunluk_tedarik_zinciri_kritik_toplanti_panosu.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/03_Hızlı Müdahale ve Problem Çözme/01_FR1 - Günlük Toplantı ve Görsel Yönetim/EKG-LOJ-PNO-01_gunluk_tedarik_zinciri_kritik_toplanti_panosu.xlsx
@@ -855,7 +855,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-PNO-01&amp;C&amp;"Arial,Regular"&amp;11Günlük Tedarik Zinciri Kritik Toplantı Panosu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Toplantı panosunda tüketim, stok, ETA ve açık risklerin tarih/sorumlu bağlantıları netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -977,7 +978,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-LOJ-PNO-01&amp;C&amp;"Arial,Regular"&amp;11Günlük Tedarik Zinciri Kritik Toplantı Panosu</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 09.06.2026 | Revizyon: 17.09.2026
+Revizyon nedeni: Toplantı panosunda tüketim, stok, ETA ve açık risklerin tarih/sorumlu bağlantıları netleştirildi.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>